--- a/2025/salida_comparativo_p11/P11_2025_comparativo_mes06_vs_mes12.xlsx
+++ b/2025/salida_comparativo_p11/P11_2025_comparativo_mes06_vs_mes12.xlsx
@@ -9744,7 +9744,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+          <t>Hospital San Juan de Dios (Santiago)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+          <t>Hospital San Juan de Dios (Santiago)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+          <t>Hospital San Juan de Dios (Santiago)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+          <t>Hospital San Juan de Dios (Santiago)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+          <t>Hospital San Juan de Dios (Santiago)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+          <t>Hospital San Juan de Dios (Santiago)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -25478,7 +25478,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -26462,7 +26462,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -27446,7 +27446,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -28922,7 +28922,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -29906,7 +29906,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -30398,7 +30398,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -30890,7 +30890,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -31382,7 +31382,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -32858,7 +32858,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -33350,7 +33350,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -33842,7 +33842,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -36235,7 +36235,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+          <t>Hospital San Juan de Dios (Santiago)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -37377,7 +37377,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -37761,7 +37761,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
